--- a/experiment_results/combined_sweep/rtt_bursts_S2_atk10pct_wu300000.xlsx
+++ b/experiment_results/combined_sweep/rtt_bursts_S2_atk10pct_wu300000.xlsx
@@ -476,22 +476,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00:009.8</t>
+          <t>00:010.0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -533,27 +533,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00:020.0</t>
+          <t>00:020.3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>100.6</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>132.4</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>11.30</t>
+          <t>32.90</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>141167</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
@@ -595,22 +595,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>104.4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>30.9</t>
+          <t>130.1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,44 +630,44 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>285366</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00:039.9</t>
+          <t>00:040.1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -677,17 +677,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1615</t>
+          <t>310298</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
@@ -709,22 +709,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>63.2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>6.48</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2182</t>
+          <t>367091</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -754,34 +754,34 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00:059.7</t>
+          <t>00:060.0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>439636</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
@@ -823,22 +823,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4362</t>
+          <t>474787</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -868,34 +868,34 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01:019.8</t>
+          <t>01:020.1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>37.4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -905,17 +905,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>6.95</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5872</t>
+          <t>474434</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -932,27 +932,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01:030.0</t>
+          <t>01:030.1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>13.89</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>495323</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -994,22 +994,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>27.5</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>7.67</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>511787</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1046,27 +1046,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01:050.2</t>
+          <t>01:050.1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>27.9</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1076,17 +1076,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6.37</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>513316</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1103,27 +1103,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>02:000.3</t>
+          <t>01:060.0</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>28.3</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>6.61</t>
+          <t>12.80</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>537779</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1153,34 +1153,34 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02:009.9</t>
+          <t>02:010.0</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>8.40</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>563023</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
@@ -1222,22 +1222,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>567162</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1274,27 +1274,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>02:030.3</t>
+          <t>02:030.0</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>8.40</t>
+          <t>11.77</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>573319</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1331,27 +1331,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>02:039.9</t>
+          <t>02:039.7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>10.44</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>569423</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1393,22 +1393,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>548920</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1450,22 +1450,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>538947</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">

--- a/experiment_results/combined_sweep/rtt_bursts_S2_atk10pct_wu300000.xlsx
+++ b/experiment_results/combined_sweep/rtt_bursts_S2_atk10pct_wu300000.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,22 +476,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00:010.0</t>
+          <t>00:010.1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>27.6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -533,27 +533,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00:020.3</t>
+          <t>00:020.2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>100.6</t>
+          <t>101.8</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>132.4</t>
+          <t>180.5</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>32.90</t>
+          <t>63.93</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>141167</t>
+          <t>143550</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -590,27 +590,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00:030.0</t>
+          <t>00:030.2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>104.4</t>
+          <t>109.8</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>130.1</t>
+          <t>175.8</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>7.15</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>285366</t>
+          <t>300908</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -647,27 +647,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00:040.1</t>
+          <t>00:040.0</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>310298</t>
+          <t>331830</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -709,22 +709,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>63.2</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>6.48</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>367091</t>
+          <t>370665</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -761,27 +761,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00:060.0</t>
+          <t>00:059.9</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>439636</t>
+          <t>398507</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -818,27 +818,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01:009.9</t>
+          <t>01:010.1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>17.34</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>474787</t>
+          <t>486943</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -875,27 +875,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01:020.1</t>
+          <t>01:019.9</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>37.4</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>138.6</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -905,17 +905,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>474434</t>
+          <t>577604</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -925,34 +925,34 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01:030.1</t>
+          <t>01:029.9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>495323</t>
+          <t>619240</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -982,34 +982,34 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01:040.0</t>
+          <t>01:040.1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>7.67</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>511787</t>
+          <t>675798</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1039,34 +1039,34 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01:050.1</t>
+          <t>01:049.9</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1076,17 +1076,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>513316</t>
+          <t>700841</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1096,34 +1096,34 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>01:060.0</t>
+          <t>02:000.2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>12.80</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>537779</t>
+          <t>710569</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1153,34 +1153,34 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>DDoS Burst</t>
+          <t>Normal/Residual</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02:010.0</t>
+          <t>02:010.1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>8.40</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>563023</t>
+          <t>732121</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>DDoS Burst</t>
+          <t>Normal/Residual</t>
         </is>
       </c>
     </row>
@@ -1222,22 +1222,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>7.66</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>567162</t>
+          <t>753263</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1274,22 +1274,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>02:030.0</t>
+          <t>02:029.9</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>11.77</t>
+          <t>15.34</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>573319</t>
+          <t>791907</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
@@ -1336,22 +1336,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>10.44</t>
+          <t>25.53</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>569423</t>
+          <t>877584</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1381,34 +1381,34 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>02:049.9</t>
+          <t>02:050.0</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>158.2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1418,17 +1418,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>12.17</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>548920</t>
+          <t>920800</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1438,44 +1438,44 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>02:055.1</t>
+          <t>02:055.4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>538947</t>
+          <t>908703</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1494,6 +1494,63 @@
         </is>
       </c>
       <c r="K19" t="inlineStr">
+        <is>
+          <t>Normal/Residual</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>03:000.5</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>29.4</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>22.4</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2.61</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>907928</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>Normal/Residual</t>
         </is>
